--- a/partial/sliding_window_results_window_6.xlsx
+++ b/partial/sliding_window_results_window_6.xlsx
@@ -463,13 +463,13 @@
         <v>29.55</v>
       </c>
       <c r="C2" t="n">
-        <v>29.84591448890856</v>
+        <v>29.34289985487003</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2959144889085614</v>
+        <v>-0.2071001451299708</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08756538474601512</v>
+        <v>0.04289047011285495</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.75</v>
       </c>
       <c r="C3" t="n">
-        <v>29.63832611849096</v>
+        <v>29.73399442021041</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1116738815090415</v>
+        <v>-0.01600557978958861</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01247105581129543</v>
+        <v>0.0002561785844008874</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.84</v>
       </c>
       <c r="C4" t="n">
-        <v>30.53792944522699</v>
+        <v>30.30976685091175</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6979294452269933</v>
+        <v>0.4697668509117463</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4871055105148586</v>
+        <v>0.2206808942155389</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.81</v>
       </c>
       <c r="C5" t="n">
-        <v>30.40112432916776</v>
+        <v>30.18441060497628</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5911243291677657</v>
+        <v>0.3744106049762763</v>
       </c>
       <c r="E5" t="n">
-        <v>0.349427972534041</v>
+        <v>0.1401833011187012</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.92</v>
       </c>
       <c r="C6" t="n">
-        <v>30.22519927145229</v>
+        <v>29.91739787915503</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3051992714522846</v>
+        <v>-0.002602120844972688</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09314659529500532</v>
+        <v>6.771032891841378e-06</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.98</v>
       </c>
       <c r="C7" t="n">
-        <v>29.60926616618648</v>
+        <v>29.86322763495295</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3707338338135209</v>
+        <v>-0.1167723650470549</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1374435755340713</v>
+        <v>0.01363578523868265</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.04</v>
       </c>
       <c r="C8" t="n">
-        <v>29.89359573285066</v>
+        <v>29.87031407170072</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.146404267149336</v>
+        <v>-0.1696859282992769</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02143420943953413</v>
+        <v>0.02879331426278733</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.21</v>
       </c>
       <c r="C9" t="n">
-        <v>29.4881873502974</v>
+        <v>29.98186659486311</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7218126497026027</v>
+        <v>-0.2281334051368944</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5210135012706922</v>
+        <v>0.05204485053935439</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.22</v>
       </c>
       <c r="C10" t="n">
-        <v>29.87883321989423</v>
+        <v>30.13287623834016</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3411667801057661</v>
+        <v>-0.08712376165983926</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1163947718477361</v>
+        <v>0.007590549845760478</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.38</v>
       </c>
       <c r="C11" t="n">
-        <v>29.73555844411813</v>
+        <v>30.19635820737606</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6444415558818726</v>
+        <v>-0.1836417926239413</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4153049189474487</v>
+        <v>0.03372430799813467</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.44</v>
       </c>
       <c r="C12" t="n">
-        <v>30.40475970552956</v>
+        <v>30.49092004476196</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03524029447044441</v>
+        <v>0.05092004476195555</v>
       </c>
       <c r="E12" t="n">
-        <v>0.001241878354363635</v>
+        <v>0.002592850958559557</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.48</v>
       </c>
       <c r="C13" t="n">
-        <v>30.33028416551723</v>
+        <v>30.41667902625066</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1497158344827696</v>
+        <v>-0.06332097374933809</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02241483109487206</v>
+        <v>0.004009545716564364</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.69</v>
       </c>
       <c r="C14" t="n">
-        <v>30.55678553735556</v>
+        <v>30.41725733225557</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1332144626444389</v>
+        <v>-0.2727426677444349</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01774609305764661</v>
+        <v>0.07438856280835121</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.75</v>
       </c>
       <c r="C15" t="n">
-        <v>30.20442464496487</v>
+        <v>30.75600763974486</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5455753550351297</v>
+        <v>0.006007639744858295</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2976524680217078</v>
+        <v>3.609173530400104e-05</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.94</v>
       </c>
       <c r="C16" t="n">
-        <v>30.62186542018789</v>
+        <v>30.8328102252049</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.31813457981211</v>
+        <v>-0.1071897747950992</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1012096108722278</v>
+        <v>0.01148964782062408</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.95</v>
       </c>
       <c r="C17" t="n">
-        <v>30.86473493105069</v>
+        <v>30.92742909302136</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08526506894930819</v>
+        <v>-0.02257090697863973</v>
       </c>
       <c r="E17" t="n">
-        <v>0.007270131982930279</v>
+        <v>0.0005094458418384075</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.02</v>
       </c>
       <c r="C18" t="n">
-        <v>31.44454446523798</v>
+        <v>31.13534542000329</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4245444652379824</v>
+        <v>0.115345420003294</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1802380029642044</v>
+        <v>0.01330456591573628</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.12</v>
       </c>
       <c r="C19" t="n">
-        <v>31.78832209817197</v>
+        <v>31.24816772355857</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6683220981719664</v>
+        <v>0.1281677235585654</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4466544269049795</v>
+        <v>0.01642696536218485</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.28</v>
       </c>
       <c r="C20" t="n">
-        <v>31.88941772239685</v>
+        <v>31.1295982748876</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6094177223968487</v>
+        <v>-0.1504017251124026</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3713899603713625</v>
+        <v>0.02262067891678671</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.38</v>
       </c>
       <c r="C21" t="n">
-        <v>31.64352926705801</v>
+        <v>30.98313353305045</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2635292670580078</v>
+        <v>-0.3968664669495467</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06944767459613081</v>
+        <v>0.1575029925890157</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.58</v>
       </c>
       <c r="C22" t="n">
-        <v>32.00931304406744</v>
+        <v>31.2016208500709</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4293130440674418</v>
+        <v>-0.3783791499290956</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1843096898064532</v>
+        <v>0.143170781101065</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.65</v>
       </c>
       <c r="C23" t="n">
-        <v>31.91376816802393</v>
+        <v>31.66159758224181</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2637681680239297</v>
+        <v>0.01159758224181573</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06957364646269999</v>
+        <v>0.0001345039138556796</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.88</v>
       </c>
       <c r="C24" t="n">
-        <v>32.52880642879173</v>
+        <v>32.49035952587511</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6488064287917332</v>
+        <v>0.6103595258751078</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4209497820414824</v>
+        <v>0.3725387508264864</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.28</v>
       </c>
       <c r="C25" t="n">
-        <v>32.30056186036718</v>
+        <v>32.47948710295107</v>
       </c>
       <c r="D25" t="n">
-        <v>0.02056186036718088</v>
+        <v>0.1994871029510676</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000422790101759444</v>
+        <v>0.03979510424380986</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.45</v>
       </c>
       <c r="C26" t="n">
-        <v>32.41812911570014</v>
+        <v>32.84956581219205</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.03187088429986318</v>
+        <v>0.3995658121920442</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001015753266055265</v>
+        <v>0.159652838272688</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.85</v>
       </c>
       <c r="C27" t="n">
-        <v>32.68084162751008</v>
+        <v>33.13122302259087</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.1691583724899246</v>
+        <v>0.2812230225908721</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02861455498344008</v>
+        <v>0.07908638843514613</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.9</v>
       </c>
       <c r="C28" t="n">
-        <v>32.83312738104019</v>
+        <v>33.19406796210896</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.06687261895981322</v>
+        <v>0.2940679621089615</v>
       </c>
       <c r="E28" t="n">
-        <v>0.004471947166544371</v>
+        <v>0.0864759663389176</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.1</v>
       </c>
       <c r="C29" t="n">
-        <v>32.90029903122721</v>
+        <v>33.31829812935527</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.1997009687727882</v>
+        <v>0.2182981293552686</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03988047692879013</v>
+        <v>0.04765407328000958</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.4</v>
       </c>
       <c r="C30" t="n">
-        <v>33.80975482240257</v>
+        <v>33.71936165410794</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4097548224025687</v>
+        <v>0.3193616541079436</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1678990144821606</v>
+        <v>0.1019918661145618</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.7</v>
       </c>
       <c r="C31" t="n">
-        <v>33.74002028657529</v>
+        <v>33.72889839495205</v>
       </c>
       <c r="D31" t="n">
-        <v>0.04002028657528456</v>
+        <v>0.02889839495205138</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001601623337567902</v>
+        <v>0.0008351172308047485</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.1</v>
       </c>
       <c r="C32" t="n">
-        <v>33.88943368249295</v>
+        <v>33.79738590116477</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.2105663175070518</v>
+        <v>-0.3026140988352282</v>
       </c>
       <c r="E32" t="n">
-        <v>0.04433817406848055</v>
+        <v>0.09157529281385723</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.4</v>
       </c>
       <c r="C33" t="n">
-        <v>34.09448789097654</v>
+        <v>34.20263769160752</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.3055121090234607</v>
+        <v>-0.1973623083924778</v>
       </c>
       <c r="E33" t="n">
-        <v>0.09333764875996295</v>
+        <v>0.03895188077400752</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.9</v>
       </c>
       <c r="C34" t="n">
-        <v>34.69025297020666</v>
+        <v>34.45974062913849</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.2097470297933413</v>
+        <v>-0.4402593708615115</v>
       </c>
       <c r="E34" t="n">
-        <v>0.04399381650712878</v>
+        <v>0.1938283136313739</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>35.3</v>
       </c>
       <c r="C35" t="n">
-        <v>35.80560405672431</v>
+        <v>35.62825551613716</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5056040567243087</v>
+        <v>0.3282555161371619</v>
       </c>
       <c r="E35" t="n">
-        <v>0.255635462176078</v>
+        <v>0.1077516838744745</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>35.7</v>
       </c>
       <c r="C36" t="n">
-        <v>36.21814574213933</v>
+        <v>35.89664932593882</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5181457421393318</v>
+        <v>0.1966493259388145</v>
       </c>
       <c r="E36" t="n">
-        <v>0.268475010097119</v>
+        <v>0.03867095739219008</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>36.3</v>
       </c>
       <c r="C37" t="n">
-        <v>36.4205231866155</v>
+        <v>36.17513560476671</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1205231866155074</v>
+        <v>-0.1248643952332884</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01452583851195643</v>
+        <v>0.01559111719697486</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>36.8</v>
       </c>
       <c r="C38" t="n">
-        <v>37.0028044816777</v>
+        <v>36.79703670043323</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2028044816777026</v>
+        <v>-0.002963299566765443</v>
       </c>
       <c r="E38" t="n">
-        <v>0.04112965778856161</v>
+        <v>8.781144322392261e-06</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>37.3</v>
       </c>
       <c r="C39" t="n">
-        <v>37.05302007412836</v>
+        <v>36.88889165364485</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.246979925871635</v>
+        <v>-0.4111083463551495</v>
       </c>
       <c r="E39" t="n">
-        <v>0.0609990837835583</v>
+        <v>0.1690100724428655</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>37.9</v>
       </c>
       <c r="C40" t="n">
-        <v>37.9774682746986</v>
+        <v>37.99193202877537</v>
       </c>
       <c r="D40" t="n">
-        <v>0.07746827469860307</v>
+        <v>0.09193202877536777</v>
       </c>
       <c r="E40" t="n">
-        <v>0.006001333584778224</v>
+        <v>0.008451497914755048</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>38.5</v>
       </c>
       <c r="C41" t="n">
-        <v>38.60024867395411</v>
+        <v>38.69646754624609</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1002486739541126</v>
+        <v>0.1964675462460903</v>
       </c>
       <c r="E41" t="n">
-        <v>0.01004979662955798</v>
+        <v>0.03859949672795963</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>38.9</v>
       </c>
       <c r="C42" t="n">
-        <v>38.99013988363992</v>
+        <v>39.00851112573505</v>
       </c>
       <c r="D42" t="n">
-        <v>0.09013988363992098</v>
+        <v>0.1085111257350562</v>
       </c>
       <c r="E42" t="n">
-        <v>0.008125198622618493</v>
+        <v>0.01177466440828917</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>39.4</v>
       </c>
       <c r="C43" t="n">
-        <v>39.40336668991242</v>
+        <v>39.37586542242229</v>
       </c>
       <c r="D43" t="n">
-        <v>0.003366689912418508</v>
+        <v>-0.02413457757771198</v>
       </c>
       <c r="E43" t="n">
-        <v>1.133460096638054e-05</v>
+        <v>0.0005824778348545979</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>39.9</v>
       </c>
       <c r="C44" t="n">
-        <v>39.68787633533997</v>
+        <v>39.6478100977316</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2121236646600266</v>
+        <v>-0.2521899022683982</v>
       </c>
       <c r="E44" t="n">
-        <v>0.04499644910879944</v>
+        <v>0.06359974680614425</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.1</v>
       </c>
       <c r="C45" t="n">
-        <v>39.81928179558339</v>
+        <v>39.85032822565149</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2807182044166083</v>
+        <v>-0.2496717743485135</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0788027102908847</v>
+        <v>0.06233599490633505</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.6</v>
       </c>
       <c r="C46" t="n">
-        <v>39.98454363845202</v>
+        <v>40.03887235974106</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.6154563615479773</v>
+        <v>-0.5611276402589382</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3787865329698746</v>
+        <v>0.3148642286625644</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.9</v>
       </c>
       <c r="C47" t="n">
-        <v>40.2827639170674</v>
+        <v>40.34758395275934</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.6172360829325996</v>
+        <v>-0.552416047240655</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3809803820739789</v>
+        <v>0.3051634892489896</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.2</v>
       </c>
       <c r="C48" t="n">
-        <v>41.1643286542588</v>
+        <v>41.43800678165266</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.03567134574120701</v>
+        <v>0.2380067816526577</v>
       </c>
       <c r="E48" t="n">
-        <v>0.001272444906988727</v>
+        <v>0.05664722811265586</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.5</v>
       </c>
       <c r="C49" t="n">
-        <v>41.38280972179857</v>
+        <v>41.53548273587013</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.1171902782014342</v>
+        <v>0.03548273587012574</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01373356130492955</v>
+        <v>0.001259024544829108</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.8</v>
       </c>
       <c r="C50" t="n">
-        <v>41.97263752137447</v>
+        <v>41.95881490504632</v>
       </c>
       <c r="D50" t="n">
-        <v>0.172637521374476</v>
+        <v>0.1588149050463272</v>
       </c>
       <c r="E50" t="n">
-        <v>0.02980371378632264</v>
+        <v>0.02522217406487393</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>42.2</v>
       </c>
       <c r="C51" t="n">
-        <v>42.53203313404133</v>
+        <v>42.78848311819058</v>
       </c>
       <c r="D51" t="n">
-        <v>0.3320331340413247</v>
+        <v>0.5884831181905739</v>
       </c>
       <c r="E51" t="n">
-        <v>0.1102460021013043</v>
+        <v>0.3463123803953009</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.8689946148521841</v>
+        <v>-0.07116797080472992</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>6.560556004411927</v>
+        <v>3.764223663269034</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.1312111200882385</v>
+        <v>0.07528447326538068</v>
       </c>
     </row>
   </sheetData>

--- a/partial/sliding_window_results_window_6.xlsx
+++ b/partial/sliding_window_results_window_6.xlsx
@@ -463,13 +463,13 @@
         <v>29.55</v>
       </c>
       <c r="C2" t="n">
-        <v>29.34289985487003</v>
+        <v>29.53798623019641</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2071001451299708</v>
+        <v>-0.01201376980359115</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04289047011285495</v>
+        <v>0.0001443306648936784</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>29.75</v>
       </c>
       <c r="C3" t="n">
-        <v>29.73399442021041</v>
+        <v>29.51863021199552</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01600557978958861</v>
+        <v>-0.2313697880044785</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002561785844008874</v>
+        <v>0.05353197880123732</v>
       </c>
     </row>
     <row r="4">
@@ -497,13 +497,13 @@
         <v>29.84</v>
       </c>
       <c r="C4" t="n">
-        <v>30.30976685091175</v>
+        <v>30.03944371107958</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4697668509117463</v>
+        <v>0.1994437110795779</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2206808942155389</v>
+        <v>0.03977779388919415</v>
       </c>
     </row>
     <row r="5">
@@ -514,13 +514,13 @@
         <v>29.81</v>
       </c>
       <c r="C5" t="n">
-        <v>30.18441060497628</v>
+        <v>29.91730429051832</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3744106049762763</v>
+        <v>0.107304290518325</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1401833011187012</v>
+        <v>0.0115142107636411</v>
       </c>
     </row>
     <row r="6">
@@ -531,13 +531,13 @@
         <v>29.92</v>
       </c>
       <c r="C6" t="n">
-        <v>29.91739787915503</v>
+        <v>29.89212441055699</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.002602120844972688</v>
+        <v>-0.02787558944300983</v>
       </c>
       <c r="E6" t="n">
-        <v>6.771032891841378e-06</v>
+        <v>0.0007770484867952411</v>
       </c>
     </row>
     <row r="7">
@@ -548,13 +548,13 @@
         <v>29.98</v>
       </c>
       <c r="C7" t="n">
-        <v>29.86322763495295</v>
+        <v>29.66891364821372</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1167723650470549</v>
+        <v>-0.3110863517862796</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01363578523868265</v>
+        <v>0.09677471826769693</v>
       </c>
     </row>
     <row r="8">
@@ -565,13 +565,13 @@
         <v>30.04</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87031407170072</v>
+        <v>29.913402274311</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1696859282992769</v>
+        <v>-0.126597725688999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02879331426278733</v>
+        <v>0.01602698414962703</v>
       </c>
     </row>
     <row r="9">
@@ -582,13 +582,13 @@
         <v>30.21</v>
       </c>
       <c r="C9" t="n">
-        <v>29.98186659486311</v>
+        <v>29.87336147646967</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2281334051368944</v>
+        <v>-0.3366385235303291</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05204485053935439</v>
+        <v>0.1133254955246799</v>
       </c>
     </row>
     <row r="10">
@@ -599,13 +599,13 @@
         <v>30.22</v>
       </c>
       <c r="C10" t="n">
-        <v>30.13287623834016</v>
+        <v>30.09576970220724</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.08712376165983926</v>
+        <v>-0.1242302977927601</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007590549845760478</v>
+        <v>0.01543316688967785</v>
       </c>
     </row>
     <row r="11">
@@ -616,13 +616,13 @@
         <v>30.38</v>
       </c>
       <c r="C11" t="n">
-        <v>30.19635820737606</v>
+        <v>30.19754879984568</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1836417926239413</v>
+        <v>-0.1824512001543219</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03372430799813467</v>
+        <v>0.03328844043775244</v>
       </c>
     </row>
     <row r="12">
@@ -633,13 +633,13 @@
         <v>30.44</v>
       </c>
       <c r="C12" t="n">
-        <v>30.49092004476196</v>
+        <v>30.60123703983972</v>
       </c>
       <c r="D12" t="n">
-        <v>0.05092004476195555</v>
+        <v>0.1612370398397225</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002592850958559557</v>
+        <v>0.02599738301627626</v>
       </c>
     </row>
     <row r="13">
@@ -650,13 +650,13 @@
         <v>30.48</v>
       </c>
       <c r="C13" t="n">
-        <v>30.41667902625066</v>
+        <v>30.40347361521986</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06332097374933809</v>
+        <v>-0.07652638478013785</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004009545716564364</v>
+        <v>0.005856287567517713</v>
       </c>
     </row>
     <row r="14">
@@ -667,13 +667,13 @@
         <v>30.69</v>
       </c>
       <c r="C14" t="n">
-        <v>30.41725733225557</v>
+        <v>30.44490582662899</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2727426677444349</v>
+        <v>-0.2450941733710117</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07438856280835121</v>
+        <v>0.06007115382041954</v>
       </c>
     </row>
     <row r="15">
@@ -684,13 +684,13 @@
         <v>30.75</v>
       </c>
       <c r="C15" t="n">
-        <v>30.75600763974486</v>
+        <v>30.58968201971004</v>
       </c>
       <c r="D15" t="n">
-        <v>0.006007639744858295</v>
+        <v>-0.1603179802899568</v>
       </c>
       <c r="E15" t="n">
-        <v>3.609173530400104e-05</v>
+        <v>0.02570185480425098</v>
       </c>
     </row>
     <row r="16">
@@ -701,13 +701,13 @@
         <v>30.94</v>
       </c>
       <c r="C16" t="n">
-        <v>30.8328102252049</v>
+        <v>30.61584367434982</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1071897747950992</v>
+        <v>-0.3241563256501792</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01148964782062408</v>
+        <v>0.105077323459025</v>
       </c>
     </row>
     <row r="17">
@@ -718,13 +718,13 @@
         <v>30.95</v>
       </c>
       <c r="C17" t="n">
-        <v>30.92742909302136</v>
+        <v>30.71504201038492</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.02257090697863973</v>
+        <v>-0.2349579896150793</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0005094458418384075</v>
+        <v>0.05520525688395971</v>
       </c>
     </row>
     <row r="18">
@@ -735,13 +735,13 @@
         <v>31.02</v>
       </c>
       <c r="C18" t="n">
-        <v>31.13534542000329</v>
+        <v>31.03800439000811</v>
       </c>
       <c r="D18" t="n">
-        <v>0.115345420003294</v>
+        <v>0.01800439000811238</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01330456591573628</v>
+        <v>0.000324158059564217</v>
       </c>
     </row>
     <row r="19">
@@ -752,13 +752,13 @@
         <v>31.12</v>
       </c>
       <c r="C19" t="n">
-        <v>31.24816772355857</v>
+        <v>31.2505268598779</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1281677235585654</v>
+        <v>0.1305268598779001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01642696536218485</v>
+        <v>0.01703726114958498</v>
       </c>
     </row>
     <row r="20">
@@ -769,13 +769,13 @@
         <v>31.28</v>
       </c>
       <c r="C20" t="n">
-        <v>31.1295982748876</v>
+        <v>31.31269394950543</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1504017251124026</v>
+        <v>0.03269394950542903</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02262067891678671</v>
+        <v>0.001068894334263543</v>
       </c>
     </row>
     <row r="21">
@@ -786,13 +786,13 @@
         <v>31.38</v>
       </c>
       <c r="C21" t="n">
-        <v>30.98313353305045</v>
+        <v>31.27426454130278</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3968664669495467</v>
+        <v>-0.1057354586972217</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1575029925890157</v>
+        <v>0.01117998722591187</v>
       </c>
     </row>
     <row r="22">
@@ -803,13 +803,13 @@
         <v>31.58</v>
       </c>
       <c r="C22" t="n">
-        <v>31.2016208500709</v>
+        <v>31.56779261274698</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3783791499290956</v>
+        <v>-0.01220738725301374</v>
       </c>
       <c r="E22" t="n">
-        <v>0.143170781101065</v>
+        <v>0.0001490203035450422</v>
       </c>
     </row>
     <row r="23">
@@ -820,13 +820,13 @@
         <v>31.65</v>
       </c>
       <c r="C23" t="n">
-        <v>31.66159758224181</v>
+        <v>31.54450298310473</v>
       </c>
       <c r="D23" t="n">
-        <v>0.01159758224181573</v>
+        <v>-0.1054970168952707</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0001345039138556796</v>
+        <v>0.01112962057380103</v>
       </c>
     </row>
     <row r="24">
@@ -837,13 +837,13 @@
         <v>31.88</v>
       </c>
       <c r="C24" t="n">
-        <v>32.49035952587511</v>
+        <v>32.12722361019225</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6103595258751078</v>
+        <v>0.247223610192254</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3725387508264864</v>
+        <v>0.06111951343649157</v>
       </c>
     </row>
     <row r="25">
@@ -854,13 +854,13 @@
         <v>32.28</v>
       </c>
       <c r="C25" t="n">
-        <v>32.47948710295107</v>
+        <v>31.98108713493898</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1994871029510676</v>
+        <v>-0.2989128650610198</v>
       </c>
       <c r="E25" t="n">
-        <v>0.03979510424380986</v>
+        <v>0.08934890089898742</v>
       </c>
     </row>
     <row r="26">
@@ -871,13 +871,13 @@
         <v>32.45</v>
       </c>
       <c r="C26" t="n">
-        <v>32.84956581219205</v>
+        <v>32.25967732137835</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3995658121920442</v>
+        <v>-0.1903226786216479</v>
       </c>
       <c r="E26" t="n">
-        <v>0.159652838272688</v>
+        <v>0.03622272199771906</v>
       </c>
     </row>
     <row r="27">
@@ -888,13 +888,13 @@
         <v>32.85</v>
       </c>
       <c r="C27" t="n">
-        <v>33.13122302259087</v>
+        <v>32.95786633927042</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2812230225908721</v>
+        <v>0.1078663392704229</v>
       </c>
       <c r="E27" t="n">
-        <v>0.07908638843514613</v>
+        <v>0.01163514714760197</v>
       </c>
     </row>
     <row r="28">
@@ -905,13 +905,13 @@
         <v>32.9</v>
       </c>
       <c r="C28" t="n">
-        <v>33.19406796210896</v>
+        <v>33.11609657900377</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2940679621089615</v>
+        <v>0.216096579003775</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0864759663389176</v>
+        <v>0.04669773145713477</v>
       </c>
     </row>
     <row r="29">
@@ -922,13 +922,13 @@
         <v>33.1</v>
       </c>
       <c r="C29" t="n">
-        <v>33.31829812935527</v>
+        <v>32.99469121095937</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2182981293552686</v>
+        <v>-0.1053087890406346</v>
       </c>
       <c r="E29" t="n">
-        <v>0.04765407328000958</v>
+        <v>0.01108994104920488</v>
       </c>
     </row>
     <row r="30">
@@ -939,13 +939,13 @@
         <v>33.4</v>
       </c>
       <c r="C30" t="n">
-        <v>33.71936165410794</v>
+        <v>33.59816370213564</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3193616541079436</v>
+        <v>0.1981637021356448</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1019918661145618</v>
+        <v>0.03926885284410456</v>
       </c>
     </row>
     <row r="31">
@@ -956,13 +956,13 @@
         <v>33.7</v>
       </c>
       <c r="C31" t="n">
-        <v>33.72889839495205</v>
+        <v>33.49970951639894</v>
       </c>
       <c r="D31" t="n">
-        <v>0.02889839495205138</v>
+        <v>-0.2002904836010657</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0008351172308047485</v>
+        <v>0.04011627782114877</v>
       </c>
     </row>
     <row r="32">
@@ -973,13 +973,13 @@
         <v>34.1</v>
       </c>
       <c r="C32" t="n">
-        <v>33.79738590116477</v>
+        <v>33.72833690060353</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.3026140988352282</v>
+        <v>-0.3716630993964714</v>
       </c>
       <c r="E32" t="n">
-        <v>0.09157529281385723</v>
+        <v>0.1381334594529914</v>
       </c>
     </row>
     <row r="33">
@@ -990,13 +990,13 @@
         <v>34.4</v>
       </c>
       <c r="C33" t="n">
-        <v>34.20263769160752</v>
+        <v>34.15104272684466</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.1973623083924778</v>
+        <v>-0.2489572731553338</v>
       </c>
       <c r="E33" t="n">
-        <v>0.03895188077400752</v>
+        <v>0.06197972385693948</v>
       </c>
     </row>
     <row r="34">
@@ -1007,13 +1007,13 @@
         <v>34.9</v>
       </c>
       <c r="C34" t="n">
-        <v>34.45974062913849</v>
+        <v>34.77386124093513</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4402593708615115</v>
+        <v>-0.1261387590648653</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1938283136313739</v>
+        <v>0.01591098653842413</v>
       </c>
     </row>
     <row r="35">
@@ -1024,13 +1024,13 @@
         <v>35.3</v>
       </c>
       <c r="C35" t="n">
-        <v>35.62825551613716</v>
+        <v>35.4444564073006</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3282555161371619</v>
+        <v>0.1444564073006021</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1077516838744745</v>
+        <v>0.02086765361019743</v>
       </c>
     </row>
     <row r="36">
@@ -1041,13 +1041,13 @@
         <v>35.7</v>
       </c>
       <c r="C36" t="n">
-        <v>35.89664932593882</v>
+        <v>35.69543437298263</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1966493259388145</v>
+        <v>-0.004565627017370844</v>
       </c>
       <c r="E36" t="n">
-        <v>0.03867095739219008</v>
+        <v>2.084495006174659e-05</v>
       </c>
     </row>
     <row r="37">
@@ -1058,13 +1058,13 @@
         <v>36.3</v>
       </c>
       <c r="C37" t="n">
-        <v>36.17513560476671</v>
+        <v>36.20940182151728</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1248643952332884</v>
+        <v>-0.09059817848271479</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01559111719697486</v>
+        <v>0.008208029944385844</v>
       </c>
     </row>
     <row r="38">
@@ -1075,13 +1075,13 @@
         <v>36.8</v>
       </c>
       <c r="C38" t="n">
-        <v>36.79703670043323</v>
+        <v>36.85601244753989</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.002963299566765443</v>
+        <v>0.05601244753989221</v>
       </c>
       <c r="E38" t="n">
-        <v>8.781144322392261e-06</v>
+        <v>0.003137394279409177</v>
       </c>
     </row>
     <row r="39">
@@ -1092,13 +1092,13 @@
         <v>37.3</v>
       </c>
       <c r="C39" t="n">
-        <v>36.88889165364485</v>
+        <v>37.01710441722531</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.4111083463551495</v>
+        <v>-0.2828955827746853</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1690100724428655</v>
+        <v>0.08002991075342882</v>
       </c>
     </row>
     <row r="40">
@@ -1109,13 +1109,13 @@
         <v>37.9</v>
       </c>
       <c r="C40" t="n">
-        <v>37.99193202877537</v>
+        <v>37.8179103598326</v>
       </c>
       <c r="D40" t="n">
-        <v>0.09193202877536777</v>
+        <v>-0.08208964016740339</v>
       </c>
       <c r="E40" t="n">
-        <v>0.008451497914755048</v>
+        <v>0.006738709022813768</v>
       </c>
     </row>
     <row r="41">
@@ -1126,13 +1126,13 @@
         <v>38.5</v>
       </c>
       <c r="C41" t="n">
-        <v>38.69646754624609</v>
+        <v>38.55676865558458</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1964675462460903</v>
+        <v>0.05676865558458388</v>
       </c>
       <c r="E41" t="n">
-        <v>0.03859949672795963</v>
+        <v>0.003222680256881107</v>
       </c>
     </row>
     <row r="42">
@@ -1143,13 +1143,13 @@
         <v>38.9</v>
       </c>
       <c r="C42" t="n">
-        <v>39.00851112573505</v>
+        <v>38.94097649683155</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1085111257350562</v>
+        <v>0.04097649683155424</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01177466440828917</v>
+        <v>0.001679073292586375</v>
       </c>
     </row>
     <row r="43">
@@ -1160,13 +1160,13 @@
         <v>39.4</v>
       </c>
       <c r="C43" t="n">
-        <v>39.37586542242229</v>
+        <v>39.31701744106033</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.02413457757771198</v>
+        <v>-0.0829825589396691</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0005824778348545979</v>
+        <v>0.006886105088175657</v>
       </c>
     </row>
     <row r="44">
@@ -1177,13 +1177,13 @@
         <v>39.9</v>
       </c>
       <c r="C44" t="n">
-        <v>39.6478100977316</v>
+        <v>39.78216155087993</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2521899022683982</v>
+        <v>-0.1178384491200646</v>
       </c>
       <c r="E44" t="n">
-        <v>0.06359974680614425</v>
+        <v>0.01388590009102205</v>
       </c>
     </row>
     <row r="45">
@@ -1194,13 +1194,13 @@
         <v>40.1</v>
       </c>
       <c r="C45" t="n">
-        <v>39.85032822565149</v>
+        <v>39.7363606715554</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2496717743485135</v>
+        <v>-0.3636393284445987</v>
       </c>
       <c r="E45" t="n">
-        <v>0.06233599490633505</v>
+        <v>0.1322335611916387</v>
       </c>
     </row>
     <row r="46">
@@ -1211,13 +1211,13 @@
         <v>40.6</v>
       </c>
       <c r="C46" t="n">
-        <v>40.03887235974106</v>
+        <v>39.8939628059572</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.5611276402589382</v>
+        <v>-0.7060371940427999</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3148642286625644</v>
+        <v>0.4984885193718302</v>
       </c>
     </row>
     <row r="47">
@@ -1228,13 +1228,13 @@
         <v>40.9</v>
       </c>
       <c r="C47" t="n">
-        <v>40.34758395275934</v>
+        <v>40.19772877847149</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.552416047240655</v>
+        <v>-0.7022712215285125</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3051634892489896</v>
+        <v>0.4931848685871491</v>
       </c>
     </row>
     <row r="48">
@@ -1245,13 +1245,13 @@
         <v>41.2</v>
       </c>
       <c r="C48" t="n">
-        <v>41.43800678165266</v>
+        <v>41.54570774344633</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2380067816526577</v>
+        <v>0.3457077434463258</v>
       </c>
       <c r="E48" t="n">
-        <v>0.05664722811265586</v>
+        <v>0.1195138438787506</v>
       </c>
     </row>
     <row r="49">
@@ -1262,13 +1262,13 @@
         <v>41.5</v>
       </c>
       <c r="C49" t="n">
-        <v>41.53548273587013</v>
+        <v>41.4503756994277</v>
       </c>
       <c r="D49" t="n">
-        <v>0.03548273587012574</v>
+        <v>-0.04962430057229739</v>
       </c>
       <c r="E49" t="n">
-        <v>0.001259024544829108</v>
+        <v>0.002462571207289715</v>
       </c>
     </row>
     <row r="50">
@@ -1279,13 +1279,13 @@
         <v>41.8</v>
       </c>
       <c r="C50" t="n">
-        <v>41.95881490504632</v>
+        <v>41.7028834706873</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1588149050463272</v>
+        <v>-0.0971165293127001</v>
       </c>
       <c r="E50" t="n">
-        <v>0.02522217406487393</v>
+        <v>0.009431620265744537</v>
       </c>
     </row>
     <row r="51">
@@ -1296,13 +1296,13 @@
         <v>42.2</v>
       </c>
       <c r="C51" t="n">
-        <v>42.78848311819058</v>
+        <v>42.64772201162574</v>
       </c>
       <c r="D51" t="n">
-        <v>0.5884831181905739</v>
+        <v>0.4477220116257357</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3463123803953009</v>
+        <v>0.2004549996941954</v>
       </c>
     </row>
     <row r="52">
@@ -1313,11 +1313,11 @@
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>-0.07116797080472992</v>
+        <v>-4.227804287339637</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>3.764223663269034</v>
+        <v>2.851361911059624</v>
       </c>
     </row>
     <row r="53">
@@ -1330,7 +1330,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>0.07528447326538068</v>
+        <v>0.05702723822119249</v>
       </c>
     </row>
   </sheetData>
